--- a/data-manipulation-scripts/sheets-cleanup/processed_sheets/CHAVETA - 23_01.xlsx
+++ b/data-manipulation-scripts/sheets-cleanup/processed_sheets/CHAVETA - 23_01.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E6"/>
+  <dimension ref="A1:D13"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -432,11 +432,6 @@
           <t>QUANTIDADE</t>
         </is>
       </c>
-      <c r="E1" t="inlineStr">
-        <is>
-          <t>PREÇO</t>
-        </is>
-      </c>
     </row>
     <row r="2">
       <c r="A2" t="n">
@@ -457,11 +452,6 @@
           <t>10</t>
         </is>
       </c>
-      <c r="E2" t="inlineStr">
-        <is>
-          <t>10</t>
-        </is>
-      </c>
     </row>
     <row r="3">
       <c r="A3" t="n">
@@ -482,11 +472,6 @@
           <t>9</t>
         </is>
       </c>
-      <c r="E3" t="inlineStr">
-        <is>
-          <t>15</t>
-        </is>
-      </c>
     </row>
     <row r="4">
       <c r="A4" t="n">
@@ -507,11 +492,6 @@
           <t>18</t>
         </is>
       </c>
-      <c r="E4" t="inlineStr">
-        <is>
-          <t>15</t>
-        </is>
-      </c>
     </row>
     <row r="5">
       <c r="A5" t="n">
@@ -528,34 +508,80 @@
         </is>
       </c>
       <c r="D5" t="inlineStr"/>
-      <c r="E5" t="inlineStr">
-        <is>
-          <t>10</t>
-        </is>
-      </c>
     </row>
     <row r="6">
       <c r="A6" t="n">
+        <v>4</v>
+      </c>
+      <c r="B6" t="inlineStr"/>
+      <c r="C6" t="inlineStr"/>
+      <c r="D6" t="inlineStr"/>
+    </row>
+    <row r="7">
+      <c r="A7" t="n">
+        <v>5</v>
+      </c>
+      <c r="B7" t="inlineStr"/>
+      <c r="C7" t="inlineStr"/>
+      <c r="D7" t="inlineStr"/>
+    </row>
+    <row r="8">
+      <c r="A8" t="n">
+        <v>6</v>
+      </c>
+      <c r="B8" t="inlineStr"/>
+      <c r="C8" t="inlineStr"/>
+      <c r="D8" t="inlineStr"/>
+    </row>
+    <row r="9">
+      <c r="A9" t="n">
+        <v>7</v>
+      </c>
+      <c r="B9" t="inlineStr"/>
+      <c r="C9" t="inlineStr"/>
+      <c r="D9" t="inlineStr"/>
+    </row>
+    <row r="10">
+      <c r="A10" t="n">
+        <v>8</v>
+      </c>
+      <c r="B10" t="inlineStr"/>
+      <c r="C10" t="inlineStr"/>
+      <c r="D10" t="inlineStr"/>
+    </row>
+    <row r="11">
+      <c r="A11" t="n">
+        <v>9</v>
+      </c>
+      <c r="B11" t="inlineStr"/>
+      <c r="C11" t="inlineStr"/>
+      <c r="D11" t="inlineStr"/>
+    </row>
+    <row r="12">
+      <c r="A12" t="n">
+        <v>10</v>
+      </c>
+      <c r="B12" t="inlineStr"/>
+      <c r="C12" t="inlineStr"/>
+      <c r="D12" t="inlineStr"/>
+    </row>
+    <row r="13">
+      <c r="A13" t="n">
         <v>11</v>
       </c>
-      <c r="B6" t="inlineStr">
+      <c r="B13" t="inlineStr">
         <is>
           <t>7893986491879</t>
         </is>
       </c>
-      <c r="C6" t="inlineStr">
+      <c r="C13" t="inlineStr">
         <is>
           <t>JOGO PRATO SEDE VALVULA C/ CHAVETA PEÇA+ CG TITAN FAN160/ BROS NXR160 2016</t>
         </is>
       </c>
-      <c r="D6" t="inlineStr">
+      <c r="D13" t="inlineStr">
         <is>
           <t>3</t>
-        </is>
-      </c>
-      <c r="E6" t="inlineStr">
-        <is>
-          <t>38</t>
         </is>
       </c>
     </row>
